--- a/data/fmsForecastOutput/File1/RPT_RPT3132569263113JV_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT3132569263113JV_fmsForecastOutput.xlsx
@@ -1878,13 +1878,13 @@
         <v>360.8432324213942</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>397.5823581854567</v>
+        <v>397.5823581854565</v>
       </c>
       <c r="E8" s="149" t="n">
         <v>436.0703541058002</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>467.6283578056763</v>
+        <v>467.6283578056762</v>
       </c>
       <c r="G8" s="150" t="n">
         <v>505.219316123881</v>
@@ -1899,7 +1899,7 @@
         <v>50.05983533348703</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>56.6164128588219</v>
+        <v>56.61641285882189</v>
       </c>
       <c r="L8" s="150" t="n">
         <v>64.93285954696171</v>
@@ -1928,13 +1928,13 @@
         <v>437.633889510427</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>482.1914287981893</v>
+        <v>482.1914287981891</v>
       </c>
       <c r="V8" s="149" t="n">
         <v>528.8700134041806</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>567.1438416583095</v>
+        <v>567.1438416583094</v>
       </c>
       <c r="X8" s="150" t="n">
         <v>612.7344910625601</v>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>843.8768162922768</v>
+        <v>843.8768162922767</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>936.5563090164418</v>
+        <v>936.556309016442</v>
       </c>
       <c r="E9" s="156" t="n">
         <v>1026.822939227442</v>
@@ -2037,16 +2037,16 @@
         <v>1146.529052835005</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>59.36287213537634</v>
+        <v>59.36287213537632</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>66.88229688076962</v>
+        <v>66.88229688076963</v>
       </c>
       <c r="J9" s="156" t="n">
         <v>76.03645831900906</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>85.21661524341901</v>
+        <v>85.216615243419</v>
       </c>
       <c r="L9" s="157" t="n">
         <v>96.89026167873936</v>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>855.9568829780013</v>
+        <v>855.9568829780011</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>949.9630793523816</v>
+        <v>949.9630793523818</v>
       </c>
       <c r="V9" s="156" t="n">
         <v>1041.521873172326</v>
@@ -2087,16 +2087,16 @@
         <v>1162.941575549185</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>59.61199779480659</v>
+        <v>59.61199779480658</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>67.1637483848064</v>
+        <v>67.16374838480641</v>
       </c>
       <c r="AA9" s="156" t="n">
         <v>76.35859284658243</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>85.58194745210344</v>
+        <v>85.58194745210342</v>
       </c>
       <c r="AC9" s="157" t="n">
         <v>97.31166476774378</v>
@@ -2173,13 +2173,13 @@
         <v>422.4284789741415</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>464.1200286038675</v>
+        <v>464.1200286038674</v>
       </c>
       <c r="E10" s="162" t="n">
         <v>508.0179470973346</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>542.5500924626086</v>
+        <v>542.5500924626085</v>
       </c>
       <c r="G10" s="163" t="n">
         <v>583.596103994775</v>
@@ -2194,7 +2194,7 @@
         <v>54.65634921982129</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>61.64721565606548</v>
+        <v>61.64721565606547</v>
       </c>
       <c r="L10" s="163" t="n">
         <v>70.51729521147682</v>
@@ -2209,7 +2209,7 @@
         <v>84704424.20462848</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>96692164.63041432</v>
+        <v>96692164.63041431</v>
       </c>
       <c r="Q10" s="166" t="n">
         <v>112276005.6846517</v>
@@ -2223,13 +2223,13 @@
         <v>499.8535852818961</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>549.6110000772017</v>
+        <v>549.6110000772015</v>
       </c>
       <c r="V10" s="162" t="n">
         <v>601.7861167785708</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>642.6793627215296</v>
+        <v>642.6793627215295</v>
       </c>
       <c r="X10" s="163" t="n">
         <v>691.2582163051453</v>
@@ -2244,7 +2244,7 @@
         <v>64.96595308458602</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>73.28500352936923</v>
+        <v>73.28500352936922</v>
       </c>
       <c r="AC10" s="163" t="n">
         <v>83.84085424871324</v>
@@ -2259,7 +2259,7 @@
         <v>84704424.20462848</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>96692164.63041432</v>
+        <v>96692164.63041431</v>
       </c>
       <c r="AH10" s="166" t="n">
         <v>112276005.6846517</v>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>862.7521669320736</v>
+        <v>862.7521669320737</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>944.4276090314042</v>
+        <v>944.4276090314044</v>
       </c>
       <c r="E11" s="156" t="n">
         <v>1026.515586749174</v>
@@ -2333,7 +2333,7 @@
         <v>1173.253128344403</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>90.3362608225179</v>
+        <v>90.33626082251791</v>
       </c>
       <c r="I11" s="156" t="n">
         <v>101.936845945489</v>
@@ -2345,22 +2345,22 @@
         <v>129.0571691126058</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>146.4987473319509</v>
+        <v>146.498747331951</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>5785673.35507804</v>
+        <v>5785673.355078041</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>6615844.72428766</v>
+        <v>6615844.724287661</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>7559820.652161693</v>
+        <v>7559820.652161695</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>8585934.018014137</v>
+        <v>8585934.018014139</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>9892432.734117649</v>
+        <v>9892432.734117651</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2389,28 +2389,28 @@
         <v>117.0125891016007</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>132.0971385558854</v>
+        <v>132.0971385558855</v>
       </c>
       <c r="AB11" s="156" t="n">
         <v>148.3327710695919</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>168.523171858905</v>
+        <v>168.5231718589051</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>5785673.35507804</v>
+        <v>5785673.355078041</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>6615844.72428766</v>
+        <v>6615844.724287661</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>7559820.652161693</v>
+        <v>7559820.652161695</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>8585934.018014137</v>
+        <v>8585934.018014139</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>9892432.734117649</v>
+        <v>9892432.734117651</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2464,16 +2464,16 @@
         <v>441.3701511308997</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>484.5670739048285</v>
+        <v>484.5670739048284</v>
       </c>
       <c r="E12" s="162" t="n">
         <v>529.9507853868778</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>565.7876120372799</v>
+        <v>565.7876120372798</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>608.3536715191437</v>
+        <v>608.3536715191439</v>
       </c>
       <c r="H12" s="161" t="n">
         <v>43.77372267350079</v>
@@ -2485,10 +2485,10 @@
         <v>57.11221157929042</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>64.39011985937819</v>
+        <v>64.39011985937817</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>73.60863337916881</v>
+        <v>73.60863337916882</v>
       </c>
       <c r="M12" s="164" t="n">
         <v>68805720.29595971</v>
@@ -2500,7 +2500,7 @@
         <v>92264244.85679018</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>105278098.6484285</v>
+        <v>105278098.6484284</v>
       </c>
       <c r="Q12" s="166" t="n">
         <v>122168438.4187693</v>
@@ -2511,34 +2511,34 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>524.1756014767423</v>
+        <v>524.1756014767421</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>575.8821471631478</v>
+        <v>575.8821471631477</v>
       </c>
       <c r="V12" s="162" t="n">
         <v>629.9963212912085</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>672.5810306721955</v>
+        <v>672.5810306721954</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>723.1249037892467</v>
+        <v>723.1249037892468</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>51.93641543461128</v>
+        <v>51.93641543461127</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>59.34107958057196</v>
+        <v>59.34107958057194</v>
       </c>
       <c r="AA12" s="162" t="n">
         <v>67.78866155393906</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>76.43903011264506</v>
+        <v>76.43903011264504</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>87.39695020932163</v>
+        <v>87.39695020932164</v>
       </c>
       <c r="AD12" s="164" t="n">
         <v>68805720.29595971</v>
@@ -2550,7 +2550,7 @@
         <v>92264244.85679018</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>105278098.6484285</v>
+        <v>105278098.6484284</v>
       </c>
       <c r="AH12" s="166" t="n">
         <v>122168438.4187693</v>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>8099.147721008589</v>
+        <v>8099.147721008587</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>8595.59864293624</v>
+        <v>8595.598642936237</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>9254.896493168326</v>
+        <v>9254.89649316832</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>9867.555400585543</v>
+        <v>9867.555400585536</v>
       </c>
       <c r="G13" s="157" t="n">
         <v>10640.47798672073</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>7992.866043197651</v>
+        <v>7992.866043197648</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>8294.827480241136</v>
+        <v>8294.827480241131</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>8839.76367552476</v>
+        <v>8839.763675524757</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>9439.616233834833</v>
+        <v>9439.616233834828</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>10207.77338497517</v>
+        <v>10207.77338497516</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>52982696.54491381</v>
+        <v>52982696.5449138</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>59526547.78476983</v>
+        <v>59526547.7847698</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>69026260.74488485</v>
+        <v>69026260.74488482</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>80046850.86192432</v>
+        <v>80046850.86192428</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>94517953.08636373</v>
+        <v>94517953.08636367</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>4547.885147046242</v>
+        <v>4547.885147046241</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>4826.655438914808</v>
+        <v>4826.655438914805</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>5196.868577856866</v>
+        <v>5196.868577856864</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>5540.892719807121</v>
+        <v>5540.892719807118</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>5974.909146027222</v>
+        <v>5974.909146027218</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>4514.179331211433</v>
+        <v>4514.179331211431</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>4730.340987965178</v>
+        <v>4730.340987965175</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>5063.34615638945</v>
+        <v>5063.346156389448</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>5403.34278580133</v>
+        <v>5403.342785801326</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>5835.995281252452</v>
+        <v>5835.995281252448</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>52982696.54491381</v>
+        <v>52982696.5449138</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>59526547.78476983</v>
+        <v>59526547.7847698</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>69026260.74488485</v>
+        <v>69026260.74488482</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>80046850.86192432</v>
+        <v>80046850.86192428</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>94517953.08636373</v>
+        <v>94517953.08636367</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,16 +2746,16 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>749.7765177413178</v>
+        <v>749.7765177413177</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>812.1354249803996</v>
+        <v>812.1354249803992</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>888.3690479504158</v>
+        <v>888.3690479504157</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>954.3699197702567</v>
+        <v>954.3699197702564</v>
       </c>
       <c r="G14" s="169" t="n">
         <v>1033.311278604459</v>
@@ -2764,10 +2764,10 @@
         <v>77.155569566373</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>86.94233652242715</v>
+        <v>86.94233652242711</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>99.35968543859742</v>
+        <v>99.3596854385974</v>
       </c>
       <c r="K14" s="168" t="n">
         <v>112.7634775504062</v>
@@ -2785,10 +2785,10 @@
         <v>161290505.601675</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>185324949.5103528</v>
+        <v>185324949.5103527</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>216686391.5051331</v>
+        <v>216686391.505133</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>852.1761661140487</v>
+        <v>852.1761661140486</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>923.5384975904618</v>
+        <v>923.538497590461</v>
       </c>
       <c r="V14" s="168" t="n">
         <v>1009.742356545031</v>
@@ -2811,7 +2811,7 @@
         <v>1172.77206040524</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>91.12190297051127</v>
+        <v>91.12190297051126</v>
       </c>
       <c r="Z14" s="168" t="n">
         <v>102.6797753070605</v>
@@ -2823,7 +2823,7 @@
         <v>133.1265298466103</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>153.2378488161949</v>
+        <v>153.2378488161948</v>
       </c>
       <c r="AD14" s="170" t="n">
         <v>121788416.8408735</v>
@@ -2835,10 +2835,10 @@
         <v>161290505.601675</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>185324949.5103528</v>
+        <v>185324949.5103527</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>216686391.5051331</v>
+        <v>216686391.505133</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>107324.8202311329</v>
       </c>
       <c r="U19" s="75" t="n">
-        <v>113866.3226073308</v>
+        <v>113866.3226073309</v>
       </c>
       <c r="V19" s="75" t="n">
         <v>120734.9965518909</v>
@@ -3706,7 +3706,7 @@
         <v>155891.1949973563</v>
       </c>
       <c r="D23" s="86" t="n">
-        <v>164552.8887516415</v>
+        <v>164552.8887516416</v>
       </c>
       <c r="E23" s="86" t="n">
         <v>174099.6473652452</v>
@@ -3742,7 +3742,7 @@
         <v>1615490.66837829</v>
       </c>
       <c r="P23" s="86" t="n">
-        <v>1635003.924178828</v>
+        <v>1635003.924178829</v>
       </c>
       <c r="Q23" s="87" t="n">
         <v>1659702.575776157</v>
@@ -3995,7 +3995,7 @@
         <v>142914.601092674</v>
       </c>
       <c r="U25" s="92" t="n">
-        <v>150793.3453267859</v>
+        <v>150793.345326786</v>
       </c>
       <c r="V25" s="92" t="n">
         <v>159734.3169336306</v>
@@ -4019,7 +4019,7 @@
         <v>1221121.238774896</v>
       </c>
       <c r="AC25" s="93" t="n">
-        <v>1229288.399375106</v>
+        <v>1229288.399375105</v>
       </c>
       <c r="AD25" s="91" t="n">
         <v>1336543.826134607</v>
@@ -4034,7 +4034,7 @@
         <v>1392096.299091443</v>
       </c>
       <c r="AH25" s="93" t="n">
-        <v>1414052.684627825</v>
+        <v>1414052.684627824</v>
       </c>
     </row>
     <row r="28" ht="1.95" customHeight="1">
@@ -4411,13 +4411,13 @@
         <v>370.9978892145276</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>418.3876078943427</v>
+        <v>418.3876078943426</v>
       </c>
       <c r="E35" s="149" t="n">
         <v>461.8198365449502</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>501.5255256500423</v>
+        <v>501.5255256500422</v>
       </c>
       <c r="G35" s="150" t="n">
         <v>543.2039160010986</v>
@@ -4432,7 +4432,7 @@
         <v>53.01581442880892</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>60.72038991108379</v>
+        <v>60.72038991108378</v>
       </c>
       <c r="L35" s="150" t="n">
         <v>69.81479618330783</v>
@@ -4461,13 +4461,13 @@
         <v>449.9495478066942</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>507.4242211419362</v>
+        <v>507.4242211419361</v>
       </c>
       <c r="V35" s="149" t="n">
         <v>560.0992152853061</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>608.254629042549</v>
+        <v>608.2546290425489</v>
       </c>
       <c r="X35" s="150" t="n">
         <v>658.8025524592366</v>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>867.9511022620007</v>
+        <v>867.9511022620006</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>985.93780968825</v>
+        <v>985.9378096882502</v>
       </c>
       <c r="E36" s="156" t="n">
         <v>1087.877721456032</v>
@@ -4525,16 +4525,16 @@
         <v>1233.226475627556</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>61.05638798055656</v>
+        <v>61.05638798055655</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>70.40877805072545</v>
+        <v>70.40877805072546</v>
       </c>
       <c r="J36" s="156" t="n">
         <v>80.55757800454428</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>91.42927303666255</v>
+        <v>91.42927303666254</v>
       </c>
       <c r="L36" s="157" t="n">
         <v>104.2168409402694</v>
@@ -4543,7 +4543,7 @@
         <v>16508976.50047516</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>19176155.71587477</v>
+        <v>19176155.71587478</v>
       </c>
       <c r="O36" s="159" t="n">
         <v>22091121.32438502</v>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>880.375791497262</v>
+        <v>880.3757914972617</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>1000.051474454324</v>
+        <v>1000.051474454325</v>
       </c>
       <c r="V36" s="156" t="n">
         <v>1103.450652442385</v>
@@ -4575,16 +4575,16 @@
         <v>1250.880068873116</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>61.3126207464409</v>
+        <v>61.31262074644089</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>70.70506955690823</v>
+        <v>70.70506955690824</v>
       </c>
       <c r="AA36" s="156" t="n">
         <v>80.89886661670023</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>91.82123953476251</v>
+        <v>91.8212395347625</v>
       </c>
       <c r="AC36" s="157" t="n">
         <v>104.6701093899318</v>
@@ -4593,7 +4593,7 @@
         <v>16508976.50047516</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>19176155.71587477</v>
+        <v>19176155.71587478</v>
       </c>
       <c r="AF36" s="159" t="n">
         <v>22091121.32438502</v>
@@ -4615,13 +4615,13 @@
         <v>434.3578442417736</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>488.4530873384646</v>
+        <v>488.4530873384645</v>
       </c>
       <c r="E37" s="162" t="n">
         <v>538.0672521757231</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>581.9331402233032</v>
+        <v>581.9331402233031</v>
       </c>
       <c r="G37" s="163" t="n">
         <v>627.5340745596224</v>
@@ -4636,7 +4636,7 @@
         <v>57.8892769570429</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>66.12211165594773</v>
+        <v>66.12211165594772</v>
       </c>
       <c r="L37" s="163" t="n">
         <v>75.82642393955733</v>
@@ -4665,13 +4665,13 @@
         <v>513.9694328062961</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>578.4262114919925</v>
+        <v>578.4262114919924</v>
       </c>
       <c r="V37" s="162" t="n">
         <v>637.3818171240811</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>689.3306717683881</v>
+        <v>689.330671768388</v>
       </c>
       <c r="X37" s="163" t="n">
         <v>743.301886495576</v>
@@ -4686,7 +4686,7 @@
         <v>68.80869477334167</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>78.604672319839</v>
+        <v>78.60467231983898</v>
       </c>
       <c r="AC37" s="163" t="n">
         <v>90.15309136081123</v>
@@ -4714,28 +4714,28 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>887.1898354573774</v>
+        <v>887.1898354573775</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>994.033275500011</v>
+        <v>994.0332755000111</v>
       </c>
       <c r="E38" s="156" t="n">
         <v>1087.344229818679</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>1172.431503804947</v>
+        <v>1172.431503804948</v>
       </c>
       <c r="G38" s="157" t="n">
         <v>1261.732447373229</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>92.89505775448769</v>
+        <v>92.89505775448771</v>
       </c>
       <c r="I38" s="156" t="n">
         <v>107.2910362852014</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>121.8341901660681</v>
+        <v>121.8341901660682</v>
       </c>
       <c r="K38" s="156" t="n">
         <v>138.4396300808439</v>
@@ -4744,19 +4744,19 @@
         <v>157.5467548670326</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>5949553.983914769</v>
+        <v>5949553.98391477</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>6963339.210538107</v>
+        <v>6963339.210538108</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>8007795.956244613</v>
+        <v>8007795.956244615</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>9210131.738712607</v>
+        <v>9210131.738712609</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>10638457.34782425</v>
+        <v>10638457.34782426</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4773,16 +4773,16 @@
         <v>1405.614962919126</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1515.607679291053</v>
+        <v>1515.607679291054</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1631.047426006133</v>
+        <v>1631.047426006134</v>
       </c>
       <c r="Y38" s="155" t="n">
         <v>106.5903767992309</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>123.1586265660869</v>
+        <v>123.158626566087</v>
       </c>
       <c r="AA38" s="156" t="n">
         <v>139.9248713204366</v>
@@ -4794,19 +4794,19 @@
         <v>181.2321219792381</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>5949553.983914769</v>
+        <v>5949553.98391477</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>6963339.210538107</v>
+        <v>6963339.210538108</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>8007795.956244613</v>
+        <v>8007795.956244615</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>9210131.738712607</v>
+        <v>9210131.738712609</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>10638457.34782425</v>
+        <v>10638457.34782426</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4816,22 +4816,22 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>453.8375936949019</v>
+        <v>453.8375936949018</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>509.9760060511064</v>
+        <v>509.9760060511063</v>
       </c>
       <c r="E39" s="162" t="n">
         <v>561.3020795028087</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>606.8625767563775</v>
+        <v>606.8625767563774</v>
       </c>
       <c r="G39" s="163" t="n">
         <v>654.161772340541</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>45.01020495905204</v>
+        <v>45.01020495905203</v>
       </c>
       <c r="I39" s="162" t="n">
         <v>52.62589319344215</v>
@@ -4840,13 +4840,13 @@
         <v>60.49090596414065</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>69.06470418256438</v>
+        <v>69.06470418256437</v>
       </c>
       <c r="L39" s="163" t="n">
         <v>79.15125086800256</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>70749284.81582293</v>
+        <v>70749284.81582291</v>
       </c>
       <c r="N39" s="165" t="n">
         <v>83918024.98973417</v>
@@ -4866,37 +4866,37 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>538.9820608354415</v>
+        <v>538.9820608354414</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>606.0793091031998</v>
+        <v>606.0793091031996</v>
       </c>
       <c r="V39" s="162" t="n">
         <v>667.266197108708</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>721.4089680781041</v>
+        <v>721.408968078104</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>777.5751028264666</v>
+        <v>777.5751028264667</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>53.4034704104679</v>
+        <v>53.40347041046789</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>62.45270962262011</v>
+        <v>62.45270962262009</v>
       </c>
       <c r="AA39" s="162" t="n">
         <v>71.79896274549471</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>81.98833942631745</v>
+        <v>81.98833942631744</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>93.97780686244901</v>
+        <v>93.97780686244903</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>70749284.81582293</v>
+        <v>70749284.81582291</v>
       </c>
       <c r="AE39" s="165" t="n">
         <v>83918024.98973417</v>
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>8330.74235857703</v>
+        <v>8330.742358577028</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>9048.951092679483</v>
+        <v>9048.951092679479</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>9805.993317618484</v>
+        <v>9805.993317618479</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>10587.50579461968</v>
+        <v>10587.50579461967</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>11445.0661360877</v>
+        <v>11445.06613608769</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>8221.421562639016</v>
+        <v>8221.421562639012</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>8732.316538836863</v>
+        <v>8732.316538836858</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>9366.140787799068</v>
+        <v>9366.140787799064</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>10128.34359853523</v>
+        <v>10128.34359853522</v>
       </c>
       <c r="L40" s="157" t="n">
         <v>10979.64223402728</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>54497733.53724935</v>
+        <v>54497733.53724933</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>62666120.41769642</v>
+        <v>62666120.41769639</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>73136533.95304604</v>
+        <v>73136533.95304601</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>85887179.0363995</v>
+        <v>85887179.03639944</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>101665002.7819337</v>
+        <v>101665002.7819336</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>4677.931646828063</v>
+        <v>4677.931646828062</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>5081.224801468374</v>
+        <v>5081.224801468371</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>5506.323985862329</v>
+        <v>5506.323985862327</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>5945.163862453994</v>
+        <v>5945.163862453989</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>6426.706621520084</v>
+        <v>6426.706621520079</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>4643.262015234965</v>
+        <v>4643.262015234964</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>4979.830495805009</v>
+        <v>4979.830495805007</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>5364.85076964341</v>
+        <v>5364.850769643408</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>5797.578096353359</v>
+        <v>5797.578096353355</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>6277.288675112888</v>
+        <v>6277.288675112884</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>54497733.53724935</v>
+        <v>54497733.53724933</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>62666120.41769642</v>
+        <v>62666120.41769639</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>73136533.95304604</v>
+        <v>73136533.95304601</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>85887179.0363995</v>
+        <v>85887179.03639944</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>101665002.7819337</v>
+        <v>101665002.7819336</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5023,13 +5023,13 @@
         <v>771.0690040494321</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>854.8270851273844</v>
+        <v>854.8270851273842</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>941.07133910366</v>
+        <v>941.0713391036597</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>1023.804975493908</v>
+        <v>1023.804975493907</v>
       </c>
       <c r="G41" s="181" t="n">
         <v>1111.261061845541</v>
@@ -5038,7 +5038,7 @@
         <v>79.34666767322724</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>91.51264902085046</v>
+        <v>91.51264902085043</v>
       </c>
       <c r="J41" s="180" t="n">
         <v>105.2541761155981</v>
@@ -5059,7 +5059,7 @@
         <v>170859028.0598639</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>198808241.3971422</v>
+        <v>198808241.3971421</v>
       </c>
       <c r="Q41" s="184" t="n">
         <v>233032537.7234623</v>
@@ -5073,7 +5073,7 @@
         <v>876.3766430825004</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>972.0863018839889</v>
+        <v>972.0863018839883</v>
       </c>
       <c r="V41" s="186" t="n">
         <v>1069.645091548208</v>
@@ -5082,19 +5082,19 @@
         <v>1162.790883237964</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>1261.24233049002</v>
+        <v>1261.242330490019</v>
       </c>
       <c r="Y41" s="185" t="n">
         <v>93.70962321175566</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>108.077360409919</v>
+        <v>108.0773604099189</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>124.289157894237</v>
+        <v>124.2891578942369</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>142.8121327000835</v>
+        <v>142.8121327000834</v>
       </c>
       <c r="AC41" s="187" t="n">
         <v>164.7976346686092</v>
@@ -5109,7 +5109,7 @@
         <v>170859028.0598639</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>198808241.3971422</v>
+        <v>198808241.3971421</v>
       </c>
       <c r="AH41" s="190" t="n">
         <v>233032537.7234623</v>
@@ -5404,7 +5404,7 @@
         <v>18668.84244629443</v>
       </c>
       <c r="N46" s="152" t="n">
-        <v>22201.83277710039</v>
+        <v>22201.83277710038</v>
       </c>
       <c r="O46" s="152" t="n">
         <v>26487.26894643421</v>
@@ -5424,7 +5424,7 @@
         <v>0.1739471112654978</v>
       </c>
       <c r="U46" s="149" t="n">
-        <v>0.1949815561679605</v>
+        <v>0.1949815561679604</v>
       </c>
       <c r="V46" s="149" t="n">
         <v>0.219383523443016</v>
@@ -5439,7 +5439,7 @@
         <v>0.01867386831113314</v>
       </c>
       <c r="Z46" s="149" t="n">
-        <v>0.02185322565295459</v>
+        <v>0.02185322565295458</v>
       </c>
       <c r="AA46" s="149" t="n">
         <v>0.02569690679835971</v>
@@ -5454,7 +5454,7 @@
         <v>18668.84244629443</v>
       </c>
       <c r="AE46" s="152" t="n">
-        <v>22201.83277710039</v>
+        <v>22201.83277710038</v>
       </c>
       <c r="AF46" s="152" t="n">
         <v>26487.26894643421</v>
@@ -5578,7 +5578,7 @@
         <v>0.1298141592574004</v>
       </c>
       <c r="D48" s="162" t="n">
-        <v>0.1455654483058414</v>
+        <v>0.1455654483058413</v>
       </c>
       <c r="E48" s="162" t="n">
         <v>0.1634668946710713</v>
@@ -5599,7 +5599,7 @@
         <v>0.01758698434193309</v>
       </c>
       <c r="K48" s="162" t="n">
-        <v>0.02068704679641598</v>
+        <v>0.02068704679641597</v>
       </c>
       <c r="L48" s="163" t="n">
         <v>0.02433832433609491</v>
@@ -5628,7 +5628,7 @@
         <v>0.1536072404084732</v>
       </c>
       <c r="U48" s="162" t="n">
-        <v>0.1723786233934422</v>
+        <v>0.1723786233934421</v>
       </c>
       <c r="V48" s="162" t="n">
         <v>0.1936390403686031</v>
@@ -5686,10 +5686,10 @@
         <v>0.2229013602642048</v>
       </c>
       <c r="F49" s="156" t="n">
-        <v>0.2321847532512753</v>
+        <v>0.2321847532512754</v>
       </c>
       <c r="G49" s="157" t="n">
-        <v>0.2416735270707882</v>
+        <v>0.2416735270707883</v>
       </c>
       <c r="H49" s="155" t="n">
         <v>0.02110910401596682</v>
@@ -5698,13 +5698,13 @@
         <v>0.02287827782156765</v>
       </c>
       <c r="J49" s="156" t="n">
-        <v>0.02497553761722078</v>
+        <v>0.02497553761722079</v>
       </c>
       <c r="K49" s="156" t="n">
         <v>0.02741616141002824</v>
       </c>
       <c r="L49" s="157" t="n">
-        <v>0.03017666701568929</v>
+        <v>0.0301766670156893</v>
       </c>
       <c r="M49" s="158" t="n">
         <v>1351.953020224044</v>
@@ -5716,7 +5716,7 @@
         <v>1641.56718950242</v>
       </c>
       <c r="P49" s="159" t="n">
-        <v>1823.946352707775</v>
+        <v>1823.946352707776</v>
       </c>
       <c r="Q49" s="160" t="n">
         <v>2037.701031778493</v>
@@ -5733,7 +5733,7 @@
         <v>0.2740060359181392</v>
       </c>
       <c r="V49" s="156" t="n">
-        <v>0.2881456291855613</v>
+        <v>0.2881456291855614</v>
       </c>
       <c r="W49" s="156" t="n">
         <v>0.3001463146460073</v>
@@ -5748,7 +5748,7 @@
         <v>0.02626181433471974</v>
       </c>
       <c r="AA49" s="156" t="n">
-        <v>0.02868405726245509</v>
+        <v>0.0286840572624551</v>
       </c>
       <c r="AB49" s="156" t="n">
         <v>0.03151095922840506</v>
@@ -5766,7 +5766,7 @@
         <v>1641.56718950242</v>
       </c>
       <c r="AG49" s="159" t="n">
-        <v>1823.946352707775</v>
+        <v>1823.946352707776</v>
       </c>
       <c r="AH49" s="160" t="n">
         <v>2037.701031778493</v>
@@ -5803,7 +5803,7 @@
         <v>0.01788759112293913</v>
       </c>
       <c r="K50" s="162" t="n">
-        <v>0.02096085379095944</v>
+        <v>0.02096085379095943</v>
       </c>
       <c r="L50" s="163" t="n">
         <v>0.02457585982742612</v>
@@ -5812,7 +5812,7 @@
         <v>20718.29505724671</v>
       </c>
       <c r="N50" s="165" t="n">
-        <v>24418.34154284851</v>
+        <v>24418.3415428485</v>
       </c>
       <c r="O50" s="165" t="n">
         <v>28897.2365388745</v>
@@ -5832,7 +5832,7 @@
         <v>0.1578360741881895</v>
       </c>
       <c r="U50" s="162" t="n">
-        <v>0.1763560519154976</v>
+        <v>0.1763560519154975</v>
       </c>
       <c r="V50" s="162" t="n">
         <v>0.1973153602810094</v>
@@ -5862,7 +5862,7 @@
         <v>20718.29505724671</v>
       </c>
       <c r="AE50" s="165" t="n">
-        <v>24418.34154284851</v>
+        <v>24418.3415428485</v>
       </c>
       <c r="AF50" s="165" t="n">
         <v>28897.2365388745</v>
@@ -6001,7 +6001,7 @@
         <v>0.01312548349876863</v>
       </c>
       <c r="I52" s="180" t="n">
-        <v>0.01524439845162595</v>
+        <v>0.01524439845162594</v>
       </c>
       <c r="J52" s="180" t="n">
         <v>0.01780154586183835</v>
@@ -6016,7 +6016,7 @@
         <v>20718.29505724671</v>
       </c>
       <c r="N52" s="183" t="n">
-        <v>24418.34154284851</v>
+        <v>24418.3415428485</v>
       </c>
       <c r="O52" s="183" t="n">
         <v>28897.2365388745</v>
@@ -6060,13 +6060,13 @@
         <v>0.02461832433914558</v>
       </c>
       <c r="AC52" s="187" t="n">
-        <v>0.02884518964597729</v>
+        <v>0.0288451896459773</v>
       </c>
       <c r="AD52" s="188" t="n">
         <v>20718.29505724671</v>
       </c>
       <c r="AE52" s="189" t="n">
-        <v>24418.34154284851</v>
+        <v>24418.3415428485</v>
       </c>
       <c r="AF52" s="189" t="n">
         <v>28897.2365388745</v>
@@ -6334,31 +6334,31 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.008182027449917724</v>
+        <v>0.008182027449917726</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.00763394075610065</v>
+        <v>0.007633940756100649</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.007123300657313041</v>
+        <v>0.007123300657313038</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.0002614860757246538</v>
+        <v>0.0002614860757246537</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.0008606729345472402</v>
+        <v>0.0008606729345472403</v>
       </c>
       <c r="I57" s="149" t="n">
         <v>0.000838450183837227</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.0008177379053139985</v>
+        <v>0.0008177379053139982</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>3.1658481298117e-05</v>
+        <v>3.165848129811698e-05</v>
       </c>
       <c r="L57" s="150" t="n">
         <v>0</v>
@@ -6373,7 +6373,7 @@
         <v>1043.054089793217</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>40.92110070816556</v>
+        <v>40.92110070816555</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.00992323584111723</v>
+        <v>0.009923235841117234</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.009258511412188589</v>
+        <v>0.009258511412188586</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.00863920254758049</v>
+        <v>0.008639202547580487</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0003171326440135655</v>
+        <v>0.0003171326440135654</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
@@ -6405,10 +6405,10 @@
         <v>0.001037679373769708</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.001011930062901882</v>
+        <v>0.001011930062901881</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>3.917092710124294e-05</v>
+        <v>3.917092710124293e-05</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
@@ -6423,7 +6423,7 @@
         <v>1043.054089793217</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>40.92110070816556</v>
+        <v>40.92110070816555</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6538,31 +6538,31 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.007138844957788517</v>
+        <v>0.007138844957788519</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.00669151184420249</v>
+        <v>0.006691511844202488</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.006255755851998042</v>
+        <v>0.006255755851998039</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.0002296126791426017</v>
+        <v>0.0002296126791426016</v>
       </c>
       <c r="G59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.0007063315740044333</v>
+        <v>0.0007063315740044334</v>
       </c>
       <c r="I59" s="162" t="n">
         <v>0.0006891700716674661</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.0006730407428209135</v>
+        <v>0.0006730407428209133</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>2.608972433166891e-05</v>
+        <v>2.60897243316689e-05</v>
       </c>
       <c r="L59" s="163" t="n">
         <v>0</v>
@@ -6577,7 +6577,7 @@
         <v>1043.054089793217</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>40.92110070816556</v>
+        <v>40.92110070816555</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.008447293268644915</v>
+        <v>0.008447293268644917</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.007924089222746214</v>
+        <v>0.007924089222746213</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.007410421311291647</v>
+        <v>0.007410421311291645</v>
       </c>
       <c r="W59" s="162" t="n">
         <v>0.000271988397669143</v>
@@ -6603,13 +6603,13 @@
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.0008392576758868207</v>
+        <v>0.0008392576758868209</v>
       </c>
       <c r="Z59" s="162" t="n">
         <v>0.0008190342564009413</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.0007999936685537253</v>
+        <v>0.000799993668553725</v>
       </c>
       <c r="AB59" s="162" t="n">
         <v>3.101495370681036e-05</v>
@@ -6627,7 +6627,7 @@
         <v>1043.054089793217</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>40.92110070816556</v>
+        <v>40.92110070816555</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.006831748918064953</v>
+        <v>0.006831748918064954</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.006406649286571114</v>
+        <v>0.006406649286571113</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.005991132696581428</v>
+        <v>0.005991132696581425</v>
       </c>
       <c r="F61" s="162" t="n">
         <v>0.0002199189779151245</v>
@@ -6757,13 +6757,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.000677551668929404</v>
+        <v>0.0006775516689294041</v>
       </c>
       <c r="I61" s="162" t="n">
         <v>0.0006611205960327989</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.0006456577621957342</v>
+        <v>0.0006456577621957338</v>
       </c>
       <c r="K61" s="162" t="n">
         <v>2.502813608151916e-05</v>
@@ -6781,7 +6781,7 @@
         <v>1043.054089793217</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>40.92110070816556</v>
+        <v>40.92110070816555</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6792,28 +6792,28 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.008113453275191534</v>
+        <v>0.008113453275191536</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.007613961298568243</v>
+        <v>0.007613961298568241</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.00712215485530109</v>
+        <v>0.007122154855301086</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.0002614290763594595</v>
+        <v>0.0002614290763594594</v>
       </c>
       <c r="X61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.0008038979279510624</v>
+        <v>0.0008038979279510625</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.0007845714363041923</v>
+        <v>0.0007845714363041922</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.0007663558162232189</v>
+        <v>0.0007663558162232186</v>
       </c>
       <c r="AB61" s="162" t="n">
         <v>2.971149070349155e-05</v>
@@ -6831,7 +6831,7 @@
         <v>1043.054089793217</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>40.92110070816556</v>
+        <v>40.92110070816555</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6946,31 +6946,31 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.006556609709307715</v>
+        <v>0.006556609709307716</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.006147913326186707</v>
+        <v>0.006147913326186706</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.005745018686957139</v>
+        <v>0.005745018686957136</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.0002107318399543441</v>
+        <v>0.000210731839954344</v>
       </c>
       <c r="G63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.0006747063219184235</v>
+        <v>0.0006747063219184236</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.0006581586430969185</v>
+        <v>0.0006581586430969184</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.0006425519336720358</v>
+        <v>0.0006425519336720355</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>2.489899839840704e-05</v>
+        <v>2.489899839840703e-05</v>
       </c>
       <c r="L63" s="181" t="n">
         <v>0</v>
@@ -6985,7 +6985,7 @@
         <v>1043.054089793217</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>40.92110070816556</v>
+        <v>40.92110070816555</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>0</v>
@@ -6999,28 +6999,28 @@
         <v>0.007452069240066164</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.006991241191972238</v>
+        <v>0.006991241191972235</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.006529931137005486</v>
+        <v>0.006529931137005483</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.0002393395892500537</v>
+        <v>0.0002393395892500536</v>
       </c>
       <c r="X63" s="187" t="n">
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.0007968384440030939</v>
+        <v>0.0007968384440030941</v>
       </c>
       <c r="Z63" s="186" t="n">
         <v>0.0007772919879161402</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.0007587560103240006</v>
+        <v>0.0007587560103240003</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>2.939530888407137e-05</v>
+        <v>2.939530888407136e-05</v>
       </c>
       <c r="AC63" s="187" t="n">
         <v>0</v>
@@ -7035,7 +7035,7 @@
         <v>1043.054089793217</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>40.92110070816556</v>
+        <v>40.92110070816555</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>0</v>
@@ -7297,43 +7297,43 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.003472795405995923</v>
+        <v>0.003472795405995924</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.005116953584883514</v>
+        <v>0.005116953584883512</v>
       </c>
       <c r="E68" s="149" t="n">
         <v>0.006822884135009854</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.008413407190420016</v>
+        <v>0.008413407190420011</v>
       </c>
       <c r="G68" s="150" t="n">
         <v>0.009940226928103991</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.0003653056692190321</v>
+        <v>0.0003653056692190322</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.0005620047117216028</v>
+        <v>0.0005620047117216027</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.0007832508059357463</v>
+        <v>0.0007832508059357462</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.001018622859566064</v>
+        <v>0.001018622859566063</v>
       </c>
       <c r="L68" s="150" t="n">
         <v>0.001277558751988093</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>452.0346736994622</v>
+        <v>452.0346736994624</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>706.6415232151752</v>
+        <v>706.6415232151751</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>999.0645549828206</v>
+        <v>999.0645549828204</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>1316.650922936778</v>
@@ -7347,43 +7347,43 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.004211837231368924</v>
+        <v>0.004211837231368925</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.00620588692981713</v>
+        <v>0.006205886929817128</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.00827485471085785</v>
+        <v>0.008274854710857848</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.01020385525334908</v>
+        <v>0.01020385525334907</v>
       </c>
       <c r="X68" s="150" t="n">
         <v>0.01205559584413177</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.0004521563665777948</v>
+        <v>0.0004521563665777949</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.0006955460307086227</v>
+        <v>0.0006955460307086226</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.0009692531459871182</v>
+        <v>0.000969253145987118</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.00126033846664954</v>
+        <v>0.001260338466649539</v>
       </c>
       <c r="AC68" s="150" t="n">
         <v>0.00158044835264979</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>452.0346736994622</v>
+        <v>452.0346736994624</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>706.6415232151752</v>
+        <v>706.6415232151751</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>999.0645549828206</v>
+        <v>999.0645549828204</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>1316.650922936778</v>
@@ -7501,16 +7501,16 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.00303002503050444</v>
+        <v>0.003030025030504441</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.004485252979219084</v>
+        <v>0.004485252979219082</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.005991926974368726</v>
+        <v>0.005991926974368725</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.007387869355399983</v>
+        <v>0.007387869355399979</v>
       </c>
       <c r="G70" s="163" t="n">
         <v>0.008725395758803515</v>
@@ -7519,25 +7519,25 @@
         <v>0.0002997967264625996</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.0004619437563744665</v>
+        <v>0.0004619437563744664</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.0006446560698927767</v>
+        <v>0.0006446560698927766</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.0008394461298936528</v>
+        <v>0.0008394461298936522</v>
       </c>
       <c r="L70" s="163" t="n">
         <v>0.001054310171621749</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>452.0346736994622</v>
+        <v>452.0346736994624</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>706.6415232151752</v>
+        <v>706.6415232151751</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>999.0645549828206</v>
+        <v>999.0645549828204</v>
       </c>
       <c r="P70" s="165" t="n">
         <v>1316.650922936778</v>
@@ -7551,43 +7551,43 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.003585385338293546</v>
+        <v>0.003585385338293547</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.005311437179135146</v>
+        <v>0.005311437179135144</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.007097895825391492</v>
+        <v>0.00709789582539149</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.008751323122344879</v>
+        <v>0.008751323122344876</v>
       </c>
       <c r="X70" s="163" t="n">
         <v>0.01033506129924575</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.0003562161358057866</v>
+        <v>0.0003562161358057867</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.0005489904111561256</v>
+        <v>0.0005489904111561255</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.000766254910731571</v>
+        <v>0.0007662549107315707</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.0009979171311676074</v>
+        <v>0.0009979171311676068</v>
       </c>
       <c r="AC70" s="163" t="n">
         <v>0.001253511853606781</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>452.0346736994622</v>
+        <v>452.0346736994624</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>706.6415232151752</v>
+        <v>706.6415232151751</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>999.0645549828206</v>
+        <v>999.0645549828204</v>
       </c>
       <c r="AG70" s="165" t="n">
         <v>1316.650922936778</v>
@@ -7603,49 +7603,49 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.01125329875724856</v>
+        <v>0.01125329875724858</v>
       </c>
       <c r="D71" s="156" t="n">
         <v>0.01685371520028444</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>0.0227071792109998</v>
+        <v>0.02270717921099981</v>
       </c>
       <c r="F71" s="156" t="n">
         <v>0.02819359390889913</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.03353583984218845</v>
+        <v>0.03353583984218846</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.001178300061839845</v>
+        <v>0.001178300061839847</v>
       </c>
       <c r="I71" s="156" t="n">
         <v>0.001819106677474751</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.002544282403180886</v>
+        <v>0.002544282403180887</v>
       </c>
       <c r="K71" s="156" t="n">
         <v>0.003329073552468165</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.004187466803978012</v>
+        <v>0.004187466803978013</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>75.46536916629029</v>
+        <v>75.46536916629036</v>
       </c>
       <c r="N71" s="159" t="n">
         <v>118.0625828027237</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>167.228052420794</v>
+        <v>167.2280524207941</v>
       </c>
       <c r="P71" s="159" t="n">
         <v>221.4770869308933</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>282.7616920903773</v>
+        <v>282.7616920903774</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7653,49 +7653,49 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.01454719184744788</v>
+        <v>0.0145471918474479</v>
       </c>
       <c r="U71" s="156" t="n">
         <v>0.02178687633284974</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>0.02935367659052172</v>
+        <v>0.02935367659052173</v>
       </c>
       <c r="W71" s="156" t="n">
         <v>0.03644599048768811</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.04335193674968971</v>
+        <v>0.04335193674968972</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.001352014311740914</v>
+        <v>0.001352014311740916</v>
       </c>
       <c r="Z71" s="156" t="n">
         <v>0.002088139771336046</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.002922072920439438</v>
+        <v>0.002922072920439439</v>
       </c>
       <c r="AB71" s="156" t="n">
         <v>0.003826294258021656</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.004817004928112026</v>
+        <v>0.004817004928112027</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>75.46536916629029</v>
+        <v>75.46536916629036</v>
       </c>
       <c r="AE71" s="159" t="n">
         <v>118.0625828027237</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>167.228052420794</v>
+        <v>167.2280524207941</v>
       </c>
       <c r="AG71" s="159" t="n">
         <v>221.4770869308933</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>282.7616920903773</v>
+        <v>282.7616920903774</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,22 +7705,22 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.003383770602789324</v>
+        <v>0.003383770602789325</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.005011787470122258</v>
+        <v>0.005011787470122256</v>
       </c>
       <c r="E72" s="162" t="n">
         <v>0.006698994656530456</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.0082662375639672</v>
+        <v>0.008266237563967197</v>
       </c>
       <c r="G72" s="163" t="n">
         <v>0.009767096644808345</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.0003355918735730628</v>
+        <v>0.0003355918735730629</v>
       </c>
       <c r="I72" s="162" t="n">
         <v>0.0005171807869024613</v>
@@ -7729,22 +7729,22 @@
         <v>0.0007219432648127873</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.0009407488184716057</v>
+        <v>0.0009407488184716052</v>
       </c>
       <c r="L72" s="163" t="n">
         <v>0.001181784001255893</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>527.5000428657526</v>
+        <v>527.5000428657527</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>824.7041060178989</v>
+        <v>824.7041060178988</v>
       </c>
       <c r="O72" s="165" t="n">
         <v>1166.292607403615</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>1538.128009867672</v>
+        <v>1538.128009867671</v>
       </c>
       <c r="Q72" s="166" t="n">
         <v>1961.40995089546</v>
@@ -7755,25 +7755,25 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.004018599777152533</v>
+        <v>0.004018599777152534</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.005956242354977323</v>
+        <v>0.005956242354977321</v>
       </c>
       <c r="V72" s="162" t="n">
         <v>0.007963648901629027</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.009826504614576022</v>
+        <v>0.009826504614576017</v>
       </c>
       <c r="X72" s="163" t="n">
         <v>0.01160974471303911</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.0003981712748621528</v>
+        <v>0.0003981712748621529</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.0006137537920371581</v>
+        <v>0.0006137537920371579</v>
       </c>
       <c r="AA72" s="162" t="n">
         <v>0.0008569019879679448</v>
@@ -7785,16 +7785,16 @@
         <v>0.00140315493950148</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>527.5000428657526</v>
+        <v>527.5000428657527</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>824.7041060178989</v>
+        <v>824.7041060178988</v>
       </c>
       <c r="AF72" s="165" t="n">
         <v>1166.292607403615</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>1538.128009867672</v>
+        <v>1538.128009867671</v>
       </c>
       <c r="AH72" s="166" t="n">
         <v>1961.40995089546</v>
@@ -7909,46 +7909,46 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.003247493936677427</v>
+        <v>0.003247493936677428</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.004809383750748595</v>
+        <v>0.004809383750748593</v>
       </c>
       <c r="E74" s="180" t="n">
         <v>0.006423801880995512</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.00792091463805736</v>
+        <v>0.007920914638057356</v>
       </c>
       <c r="G74" s="181" t="n">
         <v>0.009353365525860845</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.0003341825709646149</v>
+        <v>0.000334182570964615</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.000514863713195578</v>
+        <v>0.0005148637131955777</v>
       </c>
       <c r="J74" s="180" t="n">
         <v>0.0007184704776558234</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.0009358948364406547</v>
+        <v>0.0009358948364406542</v>
       </c>
       <c r="L74" s="181" t="n">
         <v>0.0011752274577179</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>527.5000428657526</v>
+        <v>527.5000428657527</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>824.7041060178989</v>
+        <v>824.7041060178988</v>
       </c>
       <c r="O74" s="183" t="n">
         <v>1166.292607403615</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>1538.128009867672</v>
+        <v>1538.128009867671</v>
       </c>
       <c r="Q74" s="184" t="n">
         <v>1961.40995089546</v>
@@ -7962,22 +7962,22 @@
         <v>0.003691015745295973</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.005469101466186546</v>
+        <v>0.005469101466186543</v>
       </c>
       <c r="V74" s="186" t="n">
         <v>0.007301452998908226</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.008996212705057367</v>
+        <v>0.008996212705057363</v>
       </c>
       <c r="X74" s="187" t="n">
         <v>0.01061574182593058</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.0003946747069202553</v>
+        <v>0.0003946747069202554</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.0006080592321215541</v>
+        <v>0.000608059232121554</v>
       </c>
       <c r="AA74" s="186" t="n">
         <v>0.0008484042527836479</v>
@@ -7989,16 +7989,16 @@
         <v>0.00138708406852019</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>527.5000428657526</v>
+        <v>527.5000428657527</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>824.7041060178989</v>
+        <v>824.7041060178988</v>
       </c>
       <c r="AF74" s="189" t="n">
         <v>1166.292607403615</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>1538.128009867672</v>
+        <v>1538.128009867671</v>
       </c>
       <c r="AH74" s="190" t="n">
         <v>1961.40995089546</v>
@@ -8263,13 +8263,13 @@
         <v>371.1529690312056</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>418.561127359575</v>
+        <v>418.5611273595749</v>
       </c>
       <c r="E79" s="149" t="n">
         <v>462.0146715083235</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>501.7363864187373</v>
+        <v>501.7363864187372</v>
       </c>
       <c r="G79" s="150" t="n">
         <v>543.438323936055</v>
@@ -8284,7 +8284,7 @@
         <v>53.0381810173464</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>60.74591911635309</v>
+        <v>60.74591911635308</v>
       </c>
       <c r="L79" s="150" t="n">
         <v>69.84492325294165</v>
@@ -8313,13 +8313,13 @@
         <v>450.1376299910322</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>507.6346670964462</v>
+        <v>507.634667096446</v>
       </c>
       <c r="V79" s="149" t="n">
         <v>560.3355128660077</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>608.5103628628286</v>
+        <v>608.5103628628285</v>
       </c>
       <c r="X79" s="150" t="n">
         <v>659.0868444927014</v>
@@ -8362,10 +8362,10 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>867.9877729507368</v>
+        <v>867.9877729507367</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>985.975428665936</v>
+        <v>985.9754286659362</v>
       </c>
       <c r="E80" s="156" t="n">
         <v>1087.915561349591</v>
@@ -8380,7 +8380,7 @@
         <v>61.05896759569058</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>70.41146453482652</v>
+        <v>70.41146453482654</v>
       </c>
       <c r="J80" s="156" t="n">
         <v>80.56038005675745</v>
@@ -8395,7 +8395,7 @@
         <v>16509674.00006589</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>19176887.39222077</v>
+        <v>19176887.39222078</v>
       </c>
       <c r="O80" s="159" t="n">
         <v>22091889.72478796</v>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>880.4129871256063</v>
+        <v>880.412987125606</v>
       </c>
       <c r="U80" s="156" t="n">
         <v>1000.089631946341</v>
@@ -8427,16 +8427,16 @@
         <v>1250.916483369054</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>61.31521118733686</v>
+        <v>61.31521118733684</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>70.70776734616815</v>
+        <v>70.70776734616817</v>
       </c>
       <c r="AA80" s="156" t="n">
         <v>80.90168054003136</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>91.82417409756489</v>
+        <v>91.82417409756488</v>
       </c>
       <c r="AC80" s="157" t="n">
         <v>104.6731564520507</v>
@@ -8445,7 +8445,7 @@
         <v>16509674.00006589</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>19176887.39222077</v>
+        <v>19176887.39222078</v>
       </c>
       <c r="AF80" s="159" t="n">
         <v>22091889.72478796</v>
@@ -8467,7 +8467,7 @@
         <v>434.4978272710193</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>488.6098295515937</v>
+        <v>488.6098295515936</v>
       </c>
       <c r="E81" s="162" t="n">
         <v>538.2429667532206</v>
@@ -8488,7 +8488,7 @@
         <v>57.90818163819755</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>66.14366423859838</v>
+        <v>66.14366423859836</v>
       </c>
       <c r="L81" s="163" t="n">
         <v>75.85181657406504</v>
@@ -8517,7 +8517,7 @@
         <v>514.1350727253115</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>578.6118256417877</v>
+        <v>578.6118256417876</v>
       </c>
       <c r="V81" s="162" t="n">
         <v>637.5899644815864</v>
@@ -8566,13 +8566,13 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>887.402690251104</v>
+        <v>887.4026902511041</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>994.262092583524</v>
+        <v>994.2620925835241</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>1087.589838358154</v>
+        <v>1087.589838358155</v>
       </c>
       <c r="F82" s="156" t="n">
         <v>1172.691882152108</v>
@@ -8581,31 +8581,31 @@
         <v>1262.007656740142</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>92.9173451585655</v>
+        <v>92.91734515856551</v>
       </c>
       <c r="I82" s="156" t="n">
         <v>107.3157336697005</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>121.8617099860885</v>
+        <v>121.8617099860886</v>
       </c>
       <c r="K82" s="156" t="n">
         <v>138.4703753158064</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>157.5811190008522</v>
+        <v>157.5811190008523</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>5950981.402304159</v>
+        <v>5950981.40230416</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>6964942.105540656</v>
+        <v>6964942.105540657</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>8009604.751486536</v>
+        <v>8009604.751486538</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>9212177.162152246</v>
+        <v>9212177.162152248</v>
       </c>
       <c r="Q82" s="160" t="n">
         <v>10640777.81054812</v>
@@ -8628,7 +8628,7 @@
         <v>1515.944271596187</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1631.40319043975</v>
+        <v>1631.403190439751</v>
       </c>
       <c r="Y82" s="155" t="n">
         <v>106.615949987471</v>
@@ -8637,25 +8637,25 @@
         <v>123.186976520193</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>139.9564774506194</v>
+        <v>139.9564774506195</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>159.1519062665829</v>
+        <v>159.151906266583</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>181.2716523706915</v>
+        <v>181.2716523706916</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>5950981.402304159</v>
+        <v>5950981.40230416</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>6964942.105540656</v>
+        <v>6964942.105540657</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>8009604.751486536</v>
+        <v>8009604.751486538</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>9212177.162152246</v>
+        <v>9212177.162152248</v>
       </c>
       <c r="AH82" s="160" t="n">
         <v>10640777.81054812</v>
@@ -8686,13 +8686,13 @@
         <v>45.0243989384059</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>52.64238449860646</v>
+        <v>52.64238449860647</v>
       </c>
       <c r="J83" s="162" t="n">
         <v>60.51016115629061</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>69.0866308133099</v>
+        <v>69.08663081330988</v>
       </c>
       <c r="L83" s="163" t="n">
         <v>79.17700851183125</v>
@@ -8701,7 +8701,7 @@
         <v>70771595.62042579</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>83944322.26803035</v>
+        <v>83944322.26803036</v>
       </c>
       <c r="O83" s="165" t="n">
         <v>97753600.69005394</v>
@@ -8721,7 +8721,7 @@
         <v>539.152028962682</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>606.2692353587687</v>
+        <v>606.2692353587686</v>
       </c>
       <c r="V83" s="162" t="n">
         <v>667.4785982727459</v>
@@ -8751,7 +8751,7 @@
         <v>70771595.62042579</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>83944322.26803035</v>
+        <v>83944322.26803036</v>
       </c>
       <c r="AF83" s="165" t="n">
         <v>97753600.69005394</v>
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>8330.74235857703</v>
+        <v>8330.742358577028</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>9048.951092679483</v>
+        <v>9048.951092679479</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>9805.993317618484</v>
+        <v>9805.993317618479</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>10587.50579461968</v>
+        <v>10587.50579461967</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>11445.0661360877</v>
+        <v>11445.06613608769</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>8221.421562639016</v>
+        <v>8221.421562639012</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>8732.316538836863</v>
+        <v>8732.316538836858</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>9366.140787799068</v>
+        <v>9366.140787799064</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>10128.34359853523</v>
+        <v>10128.34359853522</v>
       </c>
       <c r="L84" s="157" t="n">
         <v>10979.64223402728</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>54497733.53724935</v>
+        <v>54497733.53724933</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>62666120.41769642</v>
+        <v>62666120.41769639</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>73136533.95304604</v>
+        <v>73136533.95304601</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>85887179.0363995</v>
+        <v>85887179.03639944</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>101665002.7819337</v>
+        <v>101665002.7819336</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>4677.931646828063</v>
+        <v>4677.931646828062</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>5081.224801468374</v>
+        <v>5081.224801468371</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>5506.323985862329</v>
+        <v>5506.323985862327</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>5945.163862453994</v>
+        <v>5945.163862453989</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>6426.706621520084</v>
+        <v>6426.706621520079</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>4643.262015234965</v>
+        <v>4643.262015234964</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>4979.830495805009</v>
+        <v>4979.830495805007</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>5364.85076964341</v>
+        <v>5364.850769643408</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>5797.578096353359</v>
+        <v>5797.578096353355</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>6277.288675112888</v>
+        <v>6277.288675112884</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>54497733.53724935</v>
+        <v>54497733.53724933</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>62666120.41769642</v>
+        <v>62666120.41769639</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>73136533.95304604</v>
+        <v>73136533.95304601</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>85887179.0363995</v>
+        <v>85887179.03639944</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>101665002.7819337</v>
+        <v>101665002.7819336</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,10 +8872,10 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>771.2063579769818</v>
+        <v>771.2063579769816</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>854.9804415882091</v>
+        <v>854.980441588209</v>
       </c>
       <c r="E85" s="180" t="n">
         <v>941.2426704887984</v>
@@ -8884,22 +8884,22 @@
         <v>1023.989593286697</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>1111.464923682864</v>
+        <v>1111.464923682863</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>79.36080204561891</v>
+        <v>79.36080204561888</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>91.52906644165837</v>
+        <v>91.52906644165836</v>
       </c>
       <c r="J85" s="180" t="n">
         <v>105.2733386838713</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>120.9893827565632</v>
+        <v>120.9893827565631</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>139.6528439940566</v>
+        <v>139.6528439940565</v>
       </c>
       <c r="M85" s="182" t="n">
         <v>125269329.1576751</v>
@@ -8914,7 +8914,7 @@
         <v>198844091.5244551</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>233075287.7512708</v>
+        <v>233075287.7512707</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,22 +8922,22 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>876.5327559249414</v>
+        <v>876.5327559249412</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>972.2606947143832</v>
+        <v>972.2606947143829</v>
       </c>
       <c r="V85" s="186" t="n">
         <v>1069.839831062129</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>1163.000563686368</v>
+        <v>1163.000563686367</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>1261.473706525437</v>
+        <v>1261.473706525436</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>93.72631612085944</v>
+        <v>93.72631612085942</v>
       </c>
       <c r="Z85" s="186" t="n">
         <v>108.0967495492854</v>
@@ -8964,7 +8964,7 @@
         <v>198844091.5244551</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>233075287.7512708</v>
+        <v>233075287.7512707</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9334,7 +9334,7 @@
         <v>107324.8202311329</v>
       </c>
       <c r="U90" s="75" t="n">
-        <v>113866.3226073308</v>
+        <v>113866.3226073309</v>
       </c>
       <c r="V90" s="75" t="n">
         <v>120734.9965518909</v>
@@ -9759,7 +9759,7 @@
         <v>155891.1949973563</v>
       </c>
       <c r="D94" s="86" t="n">
-        <v>164552.8887516415</v>
+        <v>164552.8887516416</v>
       </c>
       <c r="E94" s="86" t="n">
         <v>174099.6473652452</v>
@@ -9795,7 +9795,7 @@
         <v>1615490.66837829</v>
       </c>
       <c r="P94" s="86" t="n">
-        <v>1635003.924178828</v>
+        <v>1635003.924178829</v>
       </c>
       <c r="Q94" s="87" t="n">
         <v>1659702.575776157</v>
@@ -10041,7 +10041,7 @@
         <v>142914.601092674</v>
       </c>
       <c r="U96" s="136" t="n">
-        <v>150793.3453267859</v>
+        <v>150793.345326786</v>
       </c>
       <c r="V96" s="136" t="n">
         <v>159734.3169336306</v>
@@ -10065,7 +10065,7 @@
         <v>1221121.238774896</v>
       </c>
       <c r="AC96" s="137" t="n">
-        <v>1229288.399375106</v>
+        <v>1229288.399375105</v>
       </c>
       <c r="AD96" s="135" t="n">
         <v>1336543.826134607</v>
@@ -10080,7 +10080,7 @@
         <v>1392096.299091443</v>
       </c>
       <c r="AH96" s="137" t="n">
-        <v>1414052.684627825</v>
+        <v>1414052.684627824</v>
       </c>
       <c r="AJ96" s="138" t="n"/>
       <c r="AK96" s="139" t="n"/>
